--- a/data/trans_orig/Q5403-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5403-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2007</t>
+          <t>Población según si es capaz de ir de compras en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1169</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6706</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6370</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1169</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>23021</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>32762</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29005</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>38027</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56395</t>
+          <t>56409</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69127</t>
+          <t>69022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55127</t>
+          <t>55414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64613</t>
+          <t>64653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74456</t>
+          <t>74510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88863</t>
+          <t>88822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134586</t>
+          <t>134243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151167</t>
+          <t>151203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19686</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29034</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>40990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>49147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48098</t>
+          <t>47983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>65184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93439</t>
+          <t>92836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112674</t>
+          <t>112443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>21366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47426</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54223</t>
+          <t>54281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51808</t>
+          <t>52447</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65717</t>
+          <t>66227</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102066</t>
+          <t>102534</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>117572</t>
+          <t>118390</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32932</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41508</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>55500</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>17637</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>31752</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42601</t>
+          <t>42417</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61238</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>80722</t>
+          <t>82354</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>100331</t>
+          <t>100037</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10376</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13934</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19640</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>40892</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89914</t>
+          <t>90572</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>101693</t>
+          <t>101739</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>79509</t>
+          <t>79312</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>98962</t>
+          <t>98078</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>174521</t>
+          <t>176665</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>196489</t>
+          <t>197991</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21637</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29404</t>
+          <t>31527</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>27683</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17877</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>37115</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>90981</t>
+          <t>91328</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>104246</t>
+          <t>104445</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>110190</t>
+          <t>110026</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>130206</t>
+          <t>130077</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>206637</t>
+          <t>205638</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>231361</t>
+          <t>230543</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>29372</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>72099</t>
+          <t>70741</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>60585</t>
+          <t>60298</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>93486</t>
+          <t>94026</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30079</t>
+          <t>28795</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>52318</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>77246</t>
+          <t>79436</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>114089</t>
+          <t>113814</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>114138</t>
+          <t>115493</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>158736</t>
+          <t>158559</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>426337</t>
+          <t>426981</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>454418</t>
+          <t>455129</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>502123</t>
+          <t>503019</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>548181</t>
+          <t>548479</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>941049</t>
+          <t>942631</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>993005</t>
+          <t>993334</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2012</t>
+          <t>Población según si es capaz de ir de compras en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>20162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>20725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29565</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29017</t>
+          <t>28692</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40015</t>
+          <t>39792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50002</t>
+          <t>52117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69593</t>
+          <t>70568</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>16219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30156</t>
+          <t>29832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42135</t>
+          <t>41747</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30663</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53975</t>
+          <t>53115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70362</t>
+          <t>70246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58692</t>
+          <t>59374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78128</t>
+          <t>78578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117709</t>
+          <t>119334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144195</t>
+          <t>144271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>22928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34713</t>
+          <t>34062</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48523</t>
+          <t>48261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51949</t>
+          <t>51817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67942</t>
+          <t>67132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92911</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112147</t>
+          <t>112743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26221</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25160</t>
+          <t>26476</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>17966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37561</t>
+          <t>37682</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39517</t>
+          <t>39738</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54049</t>
+          <t>54283</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48853</t>
+          <t>49173</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66735</t>
+          <t>67145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93578</t>
+          <t>94262</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116776</t>
+          <t>117177</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18594</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23263</t>
+          <t>23988</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>24568</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>38243</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48513</t>
+          <t>49061</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65194</t>
+          <t>64481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,15%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32009</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>22312</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>29080</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>43136</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>40628</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56280</t>
+          <t>56222</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>75899</t>
+          <t>75465</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95216</t>
+          <t>95840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20656</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>15386</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50280</t>
+          <t>50959</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78654</t>
+          <t>78257</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97241</t>
+          <t>97155</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,82 +8050,82 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>69,71%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>86,54%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>104383</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>92132</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>114128</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>64,9%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>80,39%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>192831</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>178099</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>205769</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>75,85%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>70,06%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>86,62%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>104383</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>92615</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>114604</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>73,53%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>80,73%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>192831</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>177266</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>205710</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>75,85%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>28702</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26648</t>
+          <t>26722</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>14873</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>35353</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>100736</t>
+          <t>99568</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>115425</t>
+          <t>115142</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>116038</t>
+          <t>116652</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>137989</t>
+          <t>138516</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>223562</t>
+          <t>221899</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>249240</t>
+          <t>250567</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>66463</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>94711</t>
+          <t>94375</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>134913</t>
+          <t>133791</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>140262</t>
+          <t>138858</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>188858</t>
+          <t>189632</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>78486</t>
+          <t>78135</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>84623</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>122985</t>
+          <t>125859</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>137760</t>
+          <t>140707</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>189132</t>
+          <t>189923</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>425811</t>
+          <t>429023</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>467905</t>
+          <t>468177</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>499770</t>
+          <t>500031</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>551107</t>
+          <t>553212</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>943890</t>
+          <t>945843</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1008006</t>
+          <t>1008660</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2016</t>
+          <t>Población según si es capaz de ir de compras en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25015</t>
+          <t>24864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28767</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27183</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35684</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33556</t>
+          <t>34268</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49849</t>
+          <t>49495</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68390</t>
+          <t>67315</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28050</t>
+          <t>27811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29565</t>
+          <t>28311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>37997</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70428</t>
+          <t>70394</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81988</t>
+          <t>81684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69053</t>
+          <t>70147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91028</t>
+          <t>91281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144740</t>
+          <t>144124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171199</t>
+          <t>169620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51111</t>
+          <t>51343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60485</t>
+          <t>60390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58910</t>
+          <t>58455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73450</t>
+          <t>73710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112906</t>
+          <t>115406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130889</t>
+          <t>131751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24212</t>
+          <t>25197</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49476</t>
+          <t>49832</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60278</t>
+          <t>60174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60532</t>
+          <t>60040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79017</t>
+          <t>79054</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>116110</t>
+          <t>115327</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>136907</t>
+          <t>136740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,49%</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>20484</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>35347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41304</t>
+          <t>41288</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>26990</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>40416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>64703</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80263</t>
+          <t>81040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14142</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>17615</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27296</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>32355</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42545</t>
+          <t>42645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43125</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58189</t>
+          <t>57751</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>79501</t>
+          <t>78856</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98238</t>
+          <t>97316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>27573</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>17482</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38670</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32960</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22446</t>
+          <t>22048</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>84916</t>
+          <t>85055</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100209</t>
+          <t>100951</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>95338</t>
+          <t>95551</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>117722</t>
+          <t>118699</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>184686</t>
+          <t>185770</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>213800</t>
+          <t>213415</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22571</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>38037</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>51057</t>
+          <t>50910</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>106898</t>
+          <t>107685</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>122560</t>
+          <t>123123</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>130486</t>
+          <t>129565</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>154739</t>
+          <t>154048</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>245522</t>
+          <t>244624</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>273311</t>
+          <t>273362</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>29224</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>50622</t>
+          <t>51283</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>51994</t>
+          <t>55252</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>90828</t>
+          <t>89855</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>90826</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>134454</t>
+          <t>132515</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>30382</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>55111</t>
+          <t>54753</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>103662</t>
+          <t>103029</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>146998</t>
+          <t>149657</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>142735</t>
+          <t>141247</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>193742</t>
+          <t>194030</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>494542</t>
+          <t>493153</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>525021</t>
+          <t>525251</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>556910</t>
+          <t>553202</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>608830</t>
+          <t>606809</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1060213</t>
+          <t>1061009</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1123214</t>
+          <t>1122936</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2023</t>
+          <t>Población según si es capaz de ir de compras en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>12823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>25130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16330</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32665</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>32295</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44361</t>
+          <t>43702</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>31320</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41983</t>
+          <t>42289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66641</t>
+          <t>66427</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83020</t>
+          <t>83122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,82 +14224,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>22014</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>29453</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>17,07%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>27135</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>20321</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>36193</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>12,99%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>22014</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>15610</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>29146</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>22,59%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>27135</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>19975</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>36030</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33460</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38679</t>
+          <t>39906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63171</t>
+          <t>63293</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74658</t>
+          <t>74656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73102</t>
+          <t>72569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89336</t>
+          <t>88885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140950</t>
+          <t>139223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161778</t>
+          <t>161340</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11023</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>21887</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20859</t>
+          <t>21704</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>35522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17950</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53452</t>
+          <t>52450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>63389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52488</t>
+          <t>51972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65226</t>
+          <t>64764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109061</t>
+          <t>108001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125578</t>
+          <t>125270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32673</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54888</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65403</t>
+          <t>65175</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72513</t>
+          <t>71625</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83398</t>
+          <t>83148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>130642</t>
+          <t>131040</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>145501</t>
+          <t>146130</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>16574</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>12759</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22537</t>
+          <t>22563</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23460</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38221</t>
+          <t>37818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46854</t>
+          <t>46461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64686</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75032</t>
+          <t>74778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19788</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11908</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41355</t>
+          <t>41029</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49832</t>
+          <t>49399</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33917</t>
+          <t>34233</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43753</t>
+          <t>43894</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>78502</t>
+          <t>77848</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>90552</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58093</t>
+          <t>59881</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>51348</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46981</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52238</t>
+          <t>51856</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>101739</t>
+          <t>101793</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114602</t>
+          <t>114575</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>238451</t>
+          <t>238167</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>329170</t>
+          <t>329120</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>362953</t>
+          <t>363194</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>444614</t>
+          <t>444907</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19451</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>33544</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>24137</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40934</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>20163</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>41969</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>38032</t>
+          <t>38028</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>57667</t>
+          <t>56741</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>121595</t>
+          <t>120913</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>134033</t>
+          <t>133330</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>117097</t>
+          <t>117085</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>135626</t>
+          <t>135818</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>243094</t>
+          <t>243977</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>266293</t>
+          <t>266456</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>36958</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>56763</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>71211</t>
+          <t>69445</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>166521</t>
+          <t>168497</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>113548</t>
+          <t>109247</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>204650</t>
+          <t>205470</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>52236</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>76474</t>
+          <t>76092</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>79936</t>
+          <t>79616</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>181288</t>
+          <t>181241</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>137152</t>
+          <t>134489</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>240065</t>
+          <t>240096</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>523808</t>
+          <t>520923</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>553785</t>
+          <t>551037</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>690602</t>
+          <t>688914</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>883502</t>
+          <t>884748</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1243298</t>
+          <t>1241326</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1432776</t>
+          <t>1438997</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
